--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,339 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120288262</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>803759</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7352629</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120288247</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>803708</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7352597</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120288263</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Valvträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>803697</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7352579</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288262</v>
+        <v>120288247</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803759</v>
+        <v>803708</v>
       </c>
       <c r="R5" t="n">
-        <v>7352629</v>
+        <v>7352597</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288247</v>
+        <v>120288262</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803708</v>
+        <v>803759</v>
       </c>
       <c r="R6" t="n">
-        <v>7352597</v>
+        <v>7352629</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1263,7 +1263,7 @@
         <v>120288263</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288262</v>
+        <v>120288263</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803759</v>
+        <v>803697</v>
       </c>
       <c r="R6" t="n">
-        <v>7352629</v>
+        <v>7352579</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288263</v>
+        <v>120288262</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>803697</v>
+        <v>803759</v>
       </c>
       <c r="R7" t="n">
-        <v>7352579</v>
+        <v>7352629</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288247</v>
+        <v>120288262</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803708</v>
+        <v>803759</v>
       </c>
       <c r="R5" t="n">
-        <v>7352597</v>
+        <v>7352629</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288262</v>
+        <v>120288247</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>803759</v>
+        <v>803708</v>
       </c>
       <c r="R7" t="n">
-        <v>7352629</v>
+        <v>7352597</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288262</v>
+        <v>120288263</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803759</v>
+        <v>803697</v>
       </c>
       <c r="R5" t="n">
-        <v>7352629</v>
+        <v>7352579</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288263</v>
+        <v>120288262</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803697</v>
+        <v>803759</v>
       </c>
       <c r="R6" t="n">
-        <v>7352579</v>
+        <v>7352629</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288263</v>
+        <v>120288247</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803697</v>
+        <v>803708</v>
       </c>
       <c r="R5" t="n">
-        <v>7352579</v>
+        <v>7352597</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288247</v>
+        <v>120288263</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>803708</v>
+        <v>803697</v>
       </c>
       <c r="R7" t="n">
-        <v>7352597</v>
+        <v>7352579</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -1038,7 +1038,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288247</v>
+        <v>120288262</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803708</v>
+        <v>803759</v>
       </c>
       <c r="R5" t="n">
-        <v>7352597</v>
+        <v>7352629</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288262</v>
+        <v>120288263</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803759</v>
+        <v>803697</v>
       </c>
       <c r="R6" t="n">
-        <v>7352629</v>
+        <v>7352579</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120288263</v>
+        <v>120288247</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>803697</v>
+        <v>803708</v>
       </c>
       <c r="R7" t="n">
-        <v>7352579</v>
+        <v>7352597</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,14 +917,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97909417</v>
+        <v>120288263</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
+        <v>98001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803696.8600712947</v>
+        <v>803697</v>
       </c>
       <c r="R4" t="n">
-        <v>7352579.332541022</v>
+        <v>7352579</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,19 +994,9 @@
           <t>2021-09-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1149,7 +1139,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120288263</v>
+        <v>120288262</v>
       </c>
       <c r="B6" t="n">
         <v>98001</v>
@@ -1193,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>803697</v>
+        <v>803759</v>
       </c>
       <c r="R6" t="n">
-        <v>7352579</v>
+        <v>7352629</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1257,117 +1247,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>120288262</v>
-      </c>
-      <c r="B7" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>803759</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7352629</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97909401</v>
+        <v>120288247</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>803708.3888110616</v>
+        <v>803708</v>
       </c>
       <c r="R2" t="n">
-        <v>7352597.296448639</v>
+        <v>7352597</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97909416</v>
+        <v>120288257</v>
       </c>
       <c r="B3" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>803758.8596788035</v>
+        <v>803725</v>
       </c>
       <c r="R3" t="n">
-        <v>7352628.848488491</v>
+        <v>7352615</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-15</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120288263</v>
+        <v>120288262</v>
       </c>
       <c r="B4" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803697</v>
+        <v>803759</v>
       </c>
       <c r="R4" t="n">
-        <v>7352579</v>
+        <v>7352629</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1028,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120288247</v>
+        <v>120288263</v>
       </c>
       <c r="B5" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803708</v>
+        <v>803697</v>
       </c>
       <c r="R5" t="n">
-        <v>7352597</v>
+        <v>7352579</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1102,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1136,117 +1096,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>120288262</v>
-      </c>
-      <c r="B6" t="n">
-        <v>98001</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Valvträsk, Nb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>803759</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7352629</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52078-2021 artfynd.xlsx
+++ b/artfynd/A 52078-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288257</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120288263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>